--- a/tools/example_framework.xlsx
+++ b/tools/example_framework.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\tools\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\tarkadia\projects\intuitem\ciso-assistant-community\tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5479025A-69C5-4707-88FE-501C490C8E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E84F6D-1951-4647-B96B-120B76A95CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="907" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1485" yWindow="-15870" windowWidth="25440" windowHeight="15990" tabRatio="907" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="info" sheetId="6" r:id="rId1"/>
@@ -169,6 +169,30 @@
     <author>.</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{940F0AB1-F4B0-4737-B66D-3373AA35955C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.: About assessable :.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Must be "x" or empty. If "x", the requirement will be assessable. </t>
+        </r>
+      </text>
+    </comment>
     <comment ref="C1" authorId="0" shapeId="0" xr:uid="{D9836FA5-3AEC-4395-A2F8-F1B7C26BF91B}">
       <text>
         <r>
@@ -189,7 +213,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The "ref_id" value can be left empty, but only if "name" is not empty.</t>
+          <t>The "ref_id" value can be left empty, but only if "name" and/or "description" is not empty.</t>
         </r>
       </text>
     </comment>
@@ -213,11 +237,92 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The "name" value can be left empty, but only if "ref_id" is not empty.</t>
+          <t>The "name" value can be left empty, but only if "ref_id" and/or "description" is not empty.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{347BCED0-BF7D-4AC6-B110-E741C99D2332}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{83FBDFDD-E613-4BF3-A6A5-A89F19C9C7AB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.: About description :.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">The </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>"description" value can be left empty, but only if "ref_id" and/or "name" is not empty.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{DB9354B9-010E-442F-98C9-17255CCA12AD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.: About importance :.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+One among "mandatory"/"recommended"/"nice to have" or empty cell (= undefined). Default value is "undefined".</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{28F2EF0B-15B6-4995-A393-1A85699772DF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.: About weight :.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Positive integer "&gt;= 1". Used for score weighting. The default weight (if undefined) is "1".</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{347BCED0-BF7D-4AC6-B110-E741C99D2332}">
       <text>
         <r>
           <rPr>
@@ -241,7 +346,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{79FD3605-3568-455D-9CFD-FA756BC48EBD}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{79FD3605-3568-455D-9CFD-FA756BC48EBD}">
       <text>
         <r>
           <rPr>
@@ -265,7 +370,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{6C4C16E2-0266-48C9-A7E3-FE00882B887F}">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{6C4C16E2-0266-48C9-A7E3-FE00882B887F}">
       <text>
         <r>
           <rPr>
@@ -289,7 +394,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{9DF94410-D1CA-448F-BD60-59EAD2557609}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{9DF94410-D1CA-448F-BD60-59EAD2557609}">
       <text>
         <r>
           <rPr>
@@ -313,7 +418,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{781B3B90-5C6F-4C56-B7DD-C93B8542FECF}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{781B3B90-5C6F-4C56-B7DD-C93B8542FECF}">
       <text>
         <r>
           <rPr>
@@ -391,7 +496,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Necessary if question_type is "unique_choice" or "multiple_choice"</t>
+          <t>Necessary if question_type is "unique_choice" or "multiple_choice". Each choice is separated by line breaks. To make a choice written on several lines, start the next line with a "|".</t>
         </r>
       </text>
     </comment>
@@ -561,7 +666,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="553">
   <si>
     <t>type</t>
   </si>
@@ -608,9 +713,6 @@
   </si>
   <si>
     <t>copyright</t>
-  </si>
-  <si>
-    <t>© Example Organization</t>
   </si>
   <si>
     <t>provider</t>
@@ -1226,9 +1328,6 @@
   </si>
   <si>
     <t>answer</t>
-  </si>
-  <si>
-    <t>Is it true ?</t>
   </si>
   <si>
     <t>Is a) respected?
@@ -1583,9 +1682,6 @@
     <t>Answers description</t>
   </si>
   <si>
-    <t>This complete example framework provides a better understanding of the structure of a CISO Assistant framework. You can convert it with "convert_library_v2.py" and add it to CISO Assistant to see how it looks like.</t>
-  </si>
-  <si>
     <t>Threats description</t>
   </si>
   <si>
@@ -1626,9 +1722,6 @@
     <t>threats</t>
   </si>
   <si>
-    <t>my-framework_example.1</t>
-  </si>
-  <si>
     <t>urn:intuitem:risk:threat:my-framework_example.1</t>
   </si>
   <si>
@@ -2419,6 +2512,34 @@
   </si>
   <si>
     <t>When creating a library, keep only the tabs that are necessary. For example, if no implementation groups are used, remove the corresponding tabs.</t>
+  </si>
+  <si>
+    <t>This complete example framework provides a better understanding of the structure of a CISO Assistant framework.
+You can convert it with "convert_library_v2.py" and add it to CISO Assistant to see how it looks like.</t>
+  </si>
+  <si>
+    <t>© 2025 Example Organization</t>
+  </si>
+  <si>
+    <t>importance</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>mandatory</t>
+  </si>
+  <si>
+    <t>recommended</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Is it true?</t>
+  </si>
+  <si>
+    <t>nice_to_have</t>
   </si>
 </sst>
 </file>
@@ -2609,18 +2730,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF5050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2700,6 +2809,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCC3399"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2881,14 +3002,14 @@
   </cellStyleXfs>
   <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2900,28 +3021,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2931,19 +3052,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2955,10 +3076,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2966,11 +3087,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2982,7 +3103,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -3024,44 +3145,44 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3073,40 +3194,22 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3116,13 +3219,76 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3134,83 +3300,38 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="65">
+  <dxfs count="67">
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -4036,6 +4157,46 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -4252,16 +4413,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{549B97EC-A4EC-467D-95D4-C91A5E59F559}" name="Tableau1" displayName="Tableau1" ref="A1:P39" totalsRowShown="0" headerRowDxfId="64" dataDxfId="62" headerRowBorderDxfId="63" tableBorderDxfId="61" totalsRowBorderDxfId="60">
-  <autoFilter ref="A1:P39" xr:uid="{549B97EC-A4EC-467D-95D4-C91A5E59F559}"/>
-  <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{D7929412-2C04-48B2-B421-6EC19B1F374C}" name="assessable" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{BAC0F5CA-29D7-460A-BD72-3F9E24C9732F}" name="depth" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{92C5BE2B-42CA-458E-8D3C-CC37002D48BD}" name="ref_id" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{9F7C5816-5FCC-476D-B6FA-AE433ADEABCC}" name="name" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{2650FBAE-CAA9-4751-AB1F-D901BDE6D752}" name="description" dataDxfId="55"/>
-    <tableColumn id="6" xr3:uid="{552D82DF-7C98-4797-9A2D-D4FDA52D98AF}" name="annotation" dataDxfId="54"/>
-    <tableColumn id="7" xr3:uid="{E61773D4-D778-4312-A49F-8A5758A995E8}" name="typical_evidence" dataDxfId="53"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{549B97EC-A4EC-467D-95D4-C91A5E59F559}" name="Tableau1" displayName="Tableau1" ref="A1:R39" totalsRowShown="0" headerRowDxfId="66" dataDxfId="64" headerRowBorderDxfId="65" tableBorderDxfId="63" totalsRowBorderDxfId="62">
+  <autoFilter ref="A1:R39" xr:uid="{549B97EC-A4EC-467D-95D4-C91A5E59F559}"/>
+  <tableColumns count="18">
+    <tableColumn id="1" xr3:uid="{D7929412-2C04-48B2-B421-6EC19B1F374C}" name="assessable" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{BAC0F5CA-29D7-460A-BD72-3F9E24C9732F}" name="depth" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{92C5BE2B-42CA-458E-8D3C-CC37002D48BD}" name="ref_id" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{9F7C5816-5FCC-476D-B6FA-AE433ADEABCC}" name="name" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{2650FBAE-CAA9-4751-AB1F-D901BDE6D752}" name="description" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{552D82DF-7C98-4797-9A2D-D4FDA52D98AF}" name="annotation" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{E61773D4-D778-4312-A49F-8A5758A995E8}" name="typical_evidence" dataDxfId="55"/>
+    <tableColumn id="18" xr3:uid="{B81C882B-0E05-4883-AAC0-A9708505EABA}" name="importance" dataDxfId="54"/>
+    <tableColumn id="17" xr3:uid="{87B98E78-198B-4AAF-BD74-A0DD4AE4E732}" name="weight" dataDxfId="53"/>
     <tableColumn id="8" xr3:uid="{41549C1C-81F1-4DC9-AF3E-D66557AB55EA}" name="implementation_groups" dataDxfId="52"/>
     <tableColumn id="14" xr3:uid="{AFF985E6-291A-441C-8DEF-8F4448E20722}" name="questions" dataDxfId="51"/>
     <tableColumn id="13" xr3:uid="{22C6C123-59A8-4006-974A-AEC9BDF7B9C5}" name="answer" dataDxfId="50"/>
@@ -4272,7 +4435,7 @@
     <tableColumn id="11" xr3:uid="{EA0E2718-3825-4A77-B686-8C594E64AC01}" name="annotation[fr]" dataDxfId="45"/>
     <tableColumn id="12" xr3:uid="{CB66FA06-DCF3-44C6-A079-7B12A457972F}" name="typical_evidence[fr]" dataDxfId="44"/>
   </tableColumns>
-  <tableStyleInfo name="Style de tableau 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -4657,380 +4820,400 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="62.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="104"/>
-      <c r="M1" s="105"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="114"/>
     </row>
     <row r="2" spans="1:13" ht="42.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="106" t="s">
-        <v>269</v>
-      </c>
-      <c r="B2" s="107"/>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="108"/>
+      <c r="A2" s="115" t="s">
+        <v>544</v>
+      </c>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="117"/>
     </row>
     <row r="3" spans="1:13" ht="34.799999999999997" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="94" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="96"/>
+    </row>
+    <row r="4" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="85" t="s">
+        <v>256</v>
+      </c>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="79" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="81"/>
+    </row>
+    <row r="5" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="90" t="s">
+        <v>257</v>
+      </c>
+      <c r="B5" s="91"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="79" t="s">
+        <v>264</v>
+      </c>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="81"/>
+    </row>
+    <row r="6" spans="1:13" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="93" t="s">
+        <v>252</v>
+      </c>
+      <c r="B6" s="93"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="79" t="s">
+        <v>265</v>
+      </c>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="81"/>
+    </row>
+    <row r="7" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="89" t="s">
+        <v>253</v>
+      </c>
+      <c r="B7" s="89"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="89"/>
+      <c r="E7" s="89"/>
+      <c r="F7" s="89"/>
+      <c r="G7" s="79" t="s">
+        <v>274</v>
+      </c>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="81"/>
+    </row>
+    <row r="8" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="88" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" s="88"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="79" t="s">
+        <v>266</v>
+      </c>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="80"/>
+      <c r="L8" s="80"/>
+      <c r="M8" s="81"/>
+    </row>
+    <row r="9" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="87" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="79" t="s">
+        <v>268</v>
+      </c>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="80"/>
+      <c r="K9" s="80"/>
+      <c r="L9" s="80"/>
+      <c r="M9" s="81"/>
+    </row>
+    <row r="10" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="82" t="s">
+        <v>271</v>
+      </c>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="79" t="s">
+        <v>267</v>
+      </c>
+      <c r="H10" s="80"/>
+      <c r="I10" s="80"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="80"/>
+      <c r="L10" s="80"/>
+      <c r="M10" s="81"/>
+    </row>
+    <row r="11" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="83" t="s">
+        <v>272</v>
+      </c>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="79" t="s">
+        <v>277</v>
+      </c>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="80"/>
+      <c r="L11" s="80"/>
+      <c r="M11" s="81"/>
+    </row>
+    <row r="12" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="84" t="s">
+        <v>273</v>
+      </c>
+      <c r="B12" s="84"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="79" t="s">
+        <v>278</v>
+      </c>
+      <c r="H12" s="80"/>
+      <c r="I12" s="80"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="80"/>
+      <c r="L12" s="80"/>
+      <c r="M12" s="81"/>
+    </row>
+    <row r="13" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="97" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="90"/>
-    </row>
-    <row r="4" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="112" t="s">
+      <c r="B13" s="97"/>
+      <c r="C13" s="98" t="s">
+        <v>543</v>
+      </c>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="99"/>
+      <c r="K13" s="99"/>
+      <c r="L13" s="99"/>
+      <c r="M13" s="99"/>
+    </row>
+    <row r="14" spans="1:13" ht="34.799999999999997" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="94" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="95"/>
+      <c r="L14" s="95"/>
+      <c r="M14" s="96"/>
+    </row>
+    <row r="15" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="109" t="s">
         <v>258</v>
       </c>
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="85" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="87"/>
-    </row>
-    <row r="5" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="94" t="s">
+      <c r="B15" s="110"/>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="79" t="s">
+        <v>263</v>
+      </c>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="81"/>
+    </row>
+    <row r="16" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="91"/>
+      <c r="C16" s="91"/>
+      <c r="D16" s="91"/>
+      <c r="E16" s="91"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="79" t="s">
         <v>259</v>
       </c>
-      <c r="B5" s="95"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="85" t="s">
-        <v>266</v>
-      </c>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="86"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="87"/>
-    </row>
-    <row r="6" spans="1:13" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="117" t="s">
-        <v>254</v>
-      </c>
-      <c r="B6" s="117"/>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="117"/>
-      <c r="G6" s="85" t="s">
-        <v>267</v>
-      </c>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="87"/>
-    </row>
-    <row r="7" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="116" t="s">
-        <v>255</v>
-      </c>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="85" t="s">
-        <v>277</v>
-      </c>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="86"/>
-      <c r="K7" s="86"/>
-      <c r="L7" s="86"/>
-      <c r="M7" s="87"/>
-    </row>
-    <row r="8" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="115" t="s">
-        <v>256</v>
-      </c>
-      <c r="B8" s="115"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="115"/>
-      <c r="E8" s="115"/>
-      <c r="F8" s="115"/>
-      <c r="G8" s="85" t="s">
-        <v>268</v>
-      </c>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="86"/>
-      <c r="K8" s="86"/>
-      <c r="L8" s="86"/>
-      <c r="M8" s="87"/>
-    </row>
-    <row r="9" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="114" t="s">
-        <v>257</v>
-      </c>
-      <c r="B9" s="114"/>
-      <c r="C9" s="114"/>
-      <c r="D9" s="114"/>
-      <c r="E9" s="114"/>
-      <c r="F9" s="114"/>
-      <c r="G9" s="85" t="s">
-        <v>271</v>
-      </c>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
-      <c r="J9" s="86"/>
-      <c r="K9" s="86"/>
-      <c r="L9" s="86"/>
-      <c r="M9" s="87"/>
-    </row>
-    <row r="10" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="109" t="s">
-        <v>274</v>
-      </c>
-      <c r="B10" s="109"/>
-      <c r="C10" s="109"/>
-      <c r="D10" s="109"/>
-      <c r="E10" s="109"/>
-      <c r="F10" s="109"/>
-      <c r="G10" s="85" t="s">
-        <v>270</v>
-      </c>
-      <c r="H10" s="86"/>
-      <c r="I10" s="86"/>
-      <c r="J10" s="86"/>
-      <c r="K10" s="86"/>
-      <c r="L10" s="86"/>
-      <c r="M10" s="87"/>
-    </row>
-    <row r="11" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="110" t="s">
-        <v>275</v>
-      </c>
-      <c r="B11" s="110"/>
-      <c r="C11" s="110"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="85" t="s">
-        <v>280</v>
-      </c>
-      <c r="H11" s="86"/>
-      <c r="I11" s="86"/>
-      <c r="J11" s="86"/>
-      <c r="K11" s="86"/>
-      <c r="L11" s="86"/>
-      <c r="M11" s="87"/>
-    </row>
-    <row r="12" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="111" t="s">
-        <v>276</v>
-      </c>
-      <c r="B12" s="111"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="85" t="s">
-        <v>281</v>
-      </c>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
-      <c r="J12" s="86"/>
-      <c r="K12" s="86"/>
-      <c r="L12" s="86"/>
-      <c r="M12" s="87"/>
-    </row>
-    <row r="13" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="79" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="79"/>
-      <c r="C13" s="80" t="s">
-        <v>547</v>
-      </c>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="81"/>
-      <c r="L13" s="81"/>
-      <c r="M13" s="81"/>
-    </row>
-    <row r="14" spans="1:13" ht="34.799999999999997" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="88" t="s">
+      <c r="H16" s="80"/>
+      <c r="I16" s="80"/>
+      <c r="J16" s="80"/>
+      <c r="K16" s="80"/>
+      <c r="L16" s="80"/>
+      <c r="M16" s="81"/>
+    </row>
+    <row r="17" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="106" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="107"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="107"/>
+      <c r="E17" s="107"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="79" t="s">
+        <v>260</v>
+      </c>
+      <c r="H17" s="80"/>
+      <c r="I17" s="80"/>
+      <c r="J17" s="80"/>
+      <c r="K17" s="80"/>
+      <c r="L17" s="80"/>
+      <c r="M17" s="81"/>
+    </row>
+    <row r="18" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="103" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="89"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="89"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="89"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="89"/>
-      <c r="K14" s="89"/>
-      <c r="L14" s="89"/>
-      <c r="M14" s="90"/>
-    </row>
-    <row r="15" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="100" t="s">
-        <v>260</v>
-      </c>
-      <c r="B15" s="101"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="102"/>
-      <c r="G15" s="85" t="s">
-        <v>265</v>
-      </c>
-      <c r="H15" s="86"/>
-      <c r="I15" s="86"/>
-      <c r="J15" s="86"/>
-      <c r="K15" s="86"/>
-      <c r="L15" s="86"/>
-      <c r="M15" s="87"/>
-    </row>
-    <row r="16" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="94" t="s">
+      <c r="B18" s="104"/>
+      <c r="C18" s="104"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="79" t="s">
+        <v>261</v>
+      </c>
+      <c r="H18" s="80"/>
+      <c r="I18" s="80"/>
+      <c r="J18" s="80"/>
+      <c r="K18" s="80"/>
+      <c r="L18" s="80"/>
+      <c r="M18" s="81"/>
+    </row>
+    <row r="19" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="100" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="85" t="s">
-        <v>261</v>
-      </c>
-      <c r="H16" s="86"/>
-      <c r="I16" s="86"/>
-      <c r="J16" s="86"/>
-      <c r="K16" s="86"/>
-      <c r="L16" s="86"/>
-      <c r="M16" s="87"/>
-    </row>
-    <row r="17" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="97" t="s">
+      <c r="B19" s="101"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="79" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="80"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="80"/>
+      <c r="L19" s="80"/>
+      <c r="M19" s="81"/>
+    </row>
+    <row r="20" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="97" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="98"/>
-      <c r="C17" s="98"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="99"/>
-      <c r="G17" s="85" t="s">
+      <c r="B20" s="97"/>
+      <c r="C20" s="98" t="s">
         <v>262</v>
       </c>
-      <c r="H17" s="86"/>
-      <c r="I17" s="86"/>
-      <c r="J17" s="86"/>
-      <c r="K17" s="86"/>
-      <c r="L17" s="86"/>
-      <c r="M17" s="87"/>
-    </row>
-    <row r="18" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="91" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="92"/>
-      <c r="C18" s="92"/>
-      <c r="D18" s="92"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="85" t="s">
-        <v>263</v>
-      </c>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="86"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="86"/>
-      <c r="M18" s="87"/>
-    </row>
-    <row r="19" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="82" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="83"/>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="84"/>
-      <c r="G19" s="85" t="s">
-        <v>48</v>
-      </c>
-      <c r="H19" s="86"/>
-      <c r="I19" s="86"/>
-      <c r="J19" s="86"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="86"/>
-      <c r="M19" s="87"/>
-    </row>
-    <row r="20" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="79" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="79"/>
-      <c r="C20" s="80" t="s">
-        <v>264</v>
-      </c>
-      <c r="D20" s="81"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="81"/>
-      <c r="I20" s="81"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="81"/>
-      <c r="L20" s="81"/>
-      <c r="M20" s="81"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="99"/>
+      <c r="H20" s="99"/>
+      <c r="I20" s="99"/>
+      <c r="J20" s="99"/>
+      <c r="K20" s="99"/>
+      <c r="L20" s="99"/>
+      <c r="M20" s="99"/>
     </row>
     <row r="21" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:M20"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="G19:M19"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:M13"/>
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="G18:M18"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="G16:M16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="G17:M17"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="G15:M15"/>
+    <mergeCell ref="G7:M7"/>
+    <mergeCell ref="G8:M8"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
     <mergeCell ref="G9:M9"/>
     <mergeCell ref="G12:M12"/>
     <mergeCell ref="G4:M4"/>
@@ -5047,26 +5230,6 @@
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="G5:M5"/>
     <mergeCell ref="G6:M6"/>
-    <mergeCell ref="G7:M7"/>
-    <mergeCell ref="G8:M8"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:M20"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="G19:M19"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:M13"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="G18:M18"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="G16:M16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="G17:M17"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="G15:M15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5090,7 +5253,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>10</v>
@@ -5099,10 +5262,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1" s="49"/>
     </row>
@@ -5111,16 +5274,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E2" s="51" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F2" s="47"/>
       <c r="G2" s="48"/>
@@ -5130,16 +5293,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D3" s="50" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E3" s="51" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F3" s="47"/>
       <c r="G3" s="48"/>
@@ -5149,16 +5312,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F4" s="47"/>
       <c r="G4" s="48"/>
@@ -5168,16 +5331,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F5" s="47"/>
       <c r="G5" s="48"/>
@@ -5187,16 +5350,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F6" s="48"/>
       <c r="G6" s="48"/>
@@ -5206,16 +5369,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F7" s="48"/>
       <c r="G7" s="48"/>
@@ -5248,15 +5411,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -5294,573 +5457,573 @@
         <v>12</v>
       </c>
       <c r="D1" s="64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E1" s="65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F1" s="65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1" s="65" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="63" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B2" s="60" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E2" s="60" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="63" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="D3" s="31"/>
       <c r="E3" s="60" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I3"/>
       <c r="J3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="63" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="31" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E4" s="60" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="I4"/>
       <c r="J4"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="63" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="E5" s="60" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="63" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B6" s="60" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
       <c r="E6" s="60" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="63" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B7" s="60" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
       <c r="E7" s="60" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="63" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B8" s="60" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
       <c r="E8" s="60" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="63" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B9" s="60" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
       <c r="E9" s="60" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="63" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C10" s="31"/>
       <c r="D10" s="31" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="63" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C11" s="31"/>
       <c r="D11" s="31" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="63" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C12" s="31"/>
       <c r="D12" s="31" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="63" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C13" s="31"/>
       <c r="D13" s="31" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="63" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D14" s="31"/>
       <c r="E14" s="31" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="63" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D15" s="31"/>
       <c r="E15" s="31" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="63" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D16" s="31"/>
       <c r="E16" s="31" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="63" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D17" s="31"/>
       <c r="E17" s="31" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="63" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D18" s="31"/>
       <c r="E18" s="31" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="63" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C19" s="31"/>
       <c r="D19" s="31"/>
       <c r="E19" s="31" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="63" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B20" s="60" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E20" s="60" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="63" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B21" s="60" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D21" s="31"/>
       <c r="E21" s="60" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="63" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B22" s="60" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C22" s="66"/>
       <c r="D22" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="E22" s="60" t="s">
+        <v>461</v>
+      </c>
+      <c r="F22" s="66" t="s">
         <v>341</v>
       </c>
-      <c r="E22" s="60" t="s">
-        <v>465</v>
-      </c>
-      <c r="F22" s="66" t="s">
-        <v>345</v>
-      </c>
       <c r="G22" s="66" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="63" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B23" s="60" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C23" s="66"/>
       <c r="D23" s="66"/>
       <c r="E23" s="60" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="F23" s="66" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G23" s="66" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="63" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B24" s="60" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C24" s="66"/>
       <c r="D24" s="66"/>
       <c r="E24" s="60" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="F24" s="66" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G24" s="66" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="63" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B25" s="60" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
       <c r="E25" s="60" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="63" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B26" s="60" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
       <c r="E26" s="60" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I26"/>
       <c r="J26"/>
@@ -5892,15 +6055,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -5935,635 +6098,635 @@
         <v>10</v>
       </c>
       <c r="C1" s="64" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D1" s="64" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E1" s="62" t="s">
         <v>12</v>
       </c>
       <c r="F1" s="74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G1" s="65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H1" s="65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I1" s="65" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
       <c r="E2" s="31" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C3" s="31"/>
       <c r="D3" s="31"/>
       <c r="E3" s="31" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="F3" s="31"/>
       <c r="G3" s="31" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="H3" s="31" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="I3" s="31"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="31" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="31"/>
       <c r="E4" s="31"/>
       <c r="F4" s="31" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="31" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D5" s="31"/>
       <c r="E5" s="31"/>
       <c r="F5" s="31"/>
       <c r="G5" s="31" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I5" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="31" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D6" s="31"/>
       <c r="E6" s="31"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="31" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D7" s="31"/>
       <c r="E7" s="31"/>
       <c r="F7" s="31"/>
       <c r="G7" s="31" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I7" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="31" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="D8" s="31"/>
       <c r="E8" s="31"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="31" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D9" s="66"/>
       <c r="E9" s="66"/>
       <c r="F9" s="66"/>
       <c r="G9" s="31" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="H9" s="66"/>
       <c r="I9" s="66"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="31" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C10" s="31"/>
       <c r="D10" s="31" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="31"/>
       <c r="G10" s="31" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I10" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="31" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C11" s="31"/>
       <c r="D11" s="31" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="31" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I11" s="31" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="31" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C12" s="31"/>
       <c r="D12" s="31" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="31" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I12" s="31" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C13" s="31"/>
       <c r="D13" s="31" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="31" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I13" s="31" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="31" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C14" s="31"/>
       <c r="D14" s="31" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="31" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I14" s="31" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="31" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C15" s="31"/>
       <c r="D15" s="31" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="F15" s="31"/>
       <c r="G15" s="31" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="I15" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="31" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="F16" s="31"/>
       <c r="G16" s="31" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="I16" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="F17" s="31"/>
       <c r="G17" s="31" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="I17" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="31" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D18" s="31"/>
       <c r="E18" s="31" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="F18" s="31"/>
       <c r="G18" s="31" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="I18" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="31" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C19" s="31"/>
       <c r="D19" s="31"/>
       <c r="E19" s="31" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="31" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="I19" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="31" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C20" s="31"/>
       <c r="D20" s="31"/>
       <c r="E20" s="31"/>
       <c r="F20" s="31"/>
       <c r="G20" s="31" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I20" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="31" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="I21" s="31" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="31" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C22" s="31"/>
       <c r="D22" s="31"/>
       <c r="E22" s="31" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="F22" s="31"/>
       <c r="G22" s="31" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="I22" s="31"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="31" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="31"/>
       <c r="F23" s="31" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I23" s="31" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="31" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C24" s="31"/>
       <c r="D24" s="31"/>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
       <c r="G24" s="31" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I24" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="31" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
       <c r="G25" s="31" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H25" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I25" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="31" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
       <c r="G26" s="31" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="H26" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I26" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="31" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C27" s="31"/>
       <c r="D27" s="31"/>
       <c r="E27" s="31"/>
       <c r="F27" s="31"/>
       <c r="G27" s="31" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I27" s="31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -6592,7 +6755,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -6614,10 +6777,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B1" s="68" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -6625,15 +6788,15 @@
         <v>5</v>
       </c>
       <c r="B2" s="67" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3" s="67" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -6641,7 +6804,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="67" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -6729,55 +6892,55 @@
         <v>14</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>15</v>
+        <v>545</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="36" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="78" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="36" t="s">
+    </row>
+    <row r="13" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="B13" s="37" t="s">
         <v>21</v>
-      </c>
-      <c r="B13" s="36" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="36" t="s">
         <v>23</v>
-      </c>
-      <c r="B14" s="36" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -6803,15 +6966,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -6819,15 +6982,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>283</v>
+      <c r="B4" s="36" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -6848,58 +7011,58 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="53" t="s">
         <v>29</v>
-      </c>
-      <c r="B7" s="53" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="52" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B9" s="54" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="52" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B10" s="55" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="52" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B11" s="55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="7" t="s">
+    </row>
+    <row r="13" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
+      <c r="B13" s="35" t="s">
         <v>21</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -6916,7 +7079,7 @@
   <sheetPr codeName="Feuil4">
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" style="29" customWidth="1"/>
@@ -6926,23 +7089,25 @@
     <col min="5" max="5" width="36.44140625" style="29" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.44140625" style="29" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.44140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.5546875" style="29" customWidth="1"/>
-    <col min="9" max="9" width="43" style="29" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" style="71" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.109375" style="71" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5546875" style="29" customWidth="1"/>
-    <col min="14" max="14" width="31.88671875" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21" style="29" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="39.21875" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.5546875" style="29" customWidth="1"/>
+    <col min="11" max="11" width="43" style="29" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5546875" style="71" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.109375" style="71" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5546875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="33.88671875" style="29" customWidth="1"/>
+    <col min="17" max="17" width="22.33203125" style="29" customWidth="1"/>
+    <col min="18" max="18" width="41.21875" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>32</v>
       </c>
       <c r="C1" s="27" t="s">
         <v>8</v>
@@ -6954,315 +7119,343 @@
         <v>12</v>
       </c>
       <c r="F1" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="J1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="K1" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="M1" s="69" t="s">
+        <v>279</v>
+      </c>
+      <c r="N1" s="75" t="s">
+        <v>388</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="J1" s="38" t="s">
-        <v>202</v>
-      </c>
-      <c r="K1" s="69" t="s">
-        <v>282</v>
-      </c>
-      <c r="L1" s="75" t="s">
-        <v>392</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="O1" s="14" t="s">
+      <c r="R1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="P1" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="39"/>
       <c r="B2" s="40">
         <v>1</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D2" s="40"/>
       <c r="E2" s="40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F2" s="40"/>
       <c r="G2" s="40"/>
       <c r="H2" s="40"/>
       <c r="I2" s="40"/>
       <c r="J2" s="40"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40" t="s">
-        <v>153</v>
-      </c>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
       <c r="O2" s="40"/>
-      <c r="P2" s="42"/>
-    </row>
-    <row r="3" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P2" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="42"/>
+    </row>
+    <row r="3" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="39"/>
       <c r="B3" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" s="40"/>
       <c r="D3" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F3" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="40" t="s">
         <v>84</v>
-      </c>
-      <c r="G3" s="40" t="s">
-        <v>85</v>
       </c>
       <c r="H3" s="40"/>
       <c r="I3" s="40"/>
       <c r="J3" s="40"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="N3" s="40" t="s">
-        <v>154</v>
-      </c>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
       <c r="O3" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="P3" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q3" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="R3" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="P3" s="40" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="39"/>
       <c r="B4" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F4" s="40"/>
       <c r="G4" s="40"/>
       <c r="H4" s="40"/>
       <c r="I4" s="40"/>
       <c r="J4" s="40"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="N4" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="O4" s="40"/>
-      <c r="P4" s="42"/>
-    </row>
-    <row r="5" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="P4" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="42"/>
+    </row>
+    <row r="5" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" s="40"/>
       <c r="D5" s="40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" s="40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40" t="s">
-        <v>203</v>
-      </c>
-      <c r="J5" s="36" t="s">
-        <v>192</v>
-      </c>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="N5" s="40" t="s">
-        <v>156</v>
-      </c>
-      <c r="O5" s="40"/>
-      <c r="P5" s="42"/>
-    </row>
-    <row r="6" spans="1:16" s="30" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H5" s="40" t="s">
+        <v>548</v>
+      </c>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40" t="s">
+        <v>551</v>
+      </c>
+      <c r="L5" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="P5" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="42"/>
+    </row>
+    <row r="6" spans="1:18" s="30" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="40"/>
       <c r="D6" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G6" s="40"/>
       <c r="H6" s="40"/>
-      <c r="I6" s="41" t="s">
-        <v>204</v>
-      </c>
-      <c r="J6" s="36" t="s">
-        <v>192</v>
-      </c>
-      <c r="K6" s="37"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="N6" s="40" t="s">
-        <v>157</v>
-      </c>
+      <c r="I6" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="40"/>
+      <c r="K6" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="L6" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="M6" s="37"/>
+      <c r="N6" s="37"/>
       <c r="O6" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="P6" s="42"/>
-    </row>
-    <row r="7" spans="1:16" s="30" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+      <c r="P6" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q6" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="R6" s="42"/>
+    </row>
+    <row r="7" spans="1:18" s="30" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" s="40"/>
       <c r="D7" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" s="40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F7" s="40"/>
       <c r="G7" s="40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H7" s="40"/>
-      <c r="I7" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="J7" s="41" t="s">
-        <v>205</v>
-      </c>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="N7" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="O7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="L7" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="40" t="s">
+        <v>132</v>
+      </c>
       <c r="P7" s="40" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" s="40"/>
       <c r="D8" s="40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" s="40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G8" s="40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H8" s="40"/>
       <c r="I8" s="40"/>
       <c r="J8" s="40"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="N8" s="40" t="s">
-        <v>159</v>
-      </c>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="41"/>
       <c r="O8" s="40" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="P8" s="40" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+      <c r="Q8" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="R8" s="40" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="40"/>
       <c r="D9" s="40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" s="40"/>
       <c r="F9" s="40"/>
       <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
+      <c r="H9" s="40" t="s">
+        <v>552</v>
+      </c>
       <c r="I9" s="40"/>
       <c r="J9" s="40"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="N9" s="40"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="42"/>
-    </row>
-    <row r="10" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="42"/>
+    </row>
+    <row r="10" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C10" s="40"/>
       <c r="D10" s="40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E10" s="40"/>
       <c r="F10" s="40"/>
@@ -7270,115 +7463,125 @@
       <c r="H10" s="40"/>
       <c r="I10" s="40"/>
       <c r="J10" s="40"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="40" t="s">
-        <v>136</v>
-      </c>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="42"/>
-    </row>
-    <row r="11" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="P10" s="40"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="42"/>
+    </row>
+    <row r="11" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C11" s="40"/>
       <c r="D11" s="40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F11" s="40"/>
       <c r="G11" s="40"/>
       <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
+      <c r="I11" s="40" t="s">
+        <v>56</v>
+      </c>
       <c r="J11" s="40"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="N11" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="O11" s="40"/>
-      <c r="P11" s="42"/>
-    </row>
-    <row r="12" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="P11" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="42"/>
+    </row>
+    <row r="12" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" s="40"/>
       <c r="D12" s="40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="40"/>
       <c r="H12" s="40"/>
       <c r="I12" s="40"/>
       <c r="J12" s="40"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="N12" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="O12" s="40"/>
-      <c r="P12" s="42"/>
-    </row>
-    <row r="13" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="P12" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="42"/>
+    </row>
+    <row r="13" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="40"/>
       <c r="H13" s="40"/>
       <c r="I13" s="40"/>
       <c r="J13" s="40"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="N13" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="O13" s="40"/>
-      <c r="P13" s="42"/>
-    </row>
-    <row r="14" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="P13" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="42"/>
+    </row>
+    <row r="14" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="39"/>
       <c r="B14" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C14" s="40"/>
       <c r="D14" s="40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" s="40"/>
       <c r="F14" s="40"/>
@@ -7386,235 +7589,255 @@
       <c r="H14" s="40"/>
       <c r="I14" s="40"/>
       <c r="J14" s="40"/>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41" t="s">
-        <v>532</v>
-      </c>
-      <c r="M14" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="42"/>
-    </row>
-    <row r="15" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K14" s="40"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41" t="s">
+        <v>528</v>
+      </c>
+      <c r="O14" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="P14" s="40"/>
+      <c r="Q14" s="40"/>
+      <c r="R14" s="42"/>
+    </row>
+    <row r="15" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C15" s="40"/>
       <c r="D15" s="40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E15" s="40"/>
       <c r="F15" s="40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G15" s="40"/>
-      <c r="H15" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="70"/>
-      <c r="L15" s="76" t="s">
-        <v>530</v>
-      </c>
-      <c r="M15" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="N15" s="40"/>
+      <c r="H15" s="39" t="s">
+        <v>549</v>
+      </c>
+      <c r="I15" s="39">
+        <v>5</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="70"/>
+      <c r="N15" s="76" t="s">
+        <v>526</v>
+      </c>
       <c r="O15" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="P15" s="42"/>
-    </row>
-    <row r="16" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="R15" s="42"/>
+    </row>
+    <row r="16" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="40" t="s">
         <v>68</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="40" t="s">
-        <v>69</v>
       </c>
       <c r="E16" s="40"/>
       <c r="F16" s="40"/>
       <c r="G16" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="70"/>
-      <c r="L16" s="70" t="s">
-        <v>531</v>
-      </c>
-      <c r="M16" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" s="30" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>549</v>
+      </c>
+      <c r="I16" s="39"/>
+      <c r="J16" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="70"/>
+      <c r="N16" s="70" t="s">
+        <v>527</v>
+      </c>
+      <c r="O16" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="40" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" s="30" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E17" s="40"/>
       <c r="F17" s="40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="70"/>
-      <c r="L17" s="70" t="s">
-        <v>533</v>
-      </c>
-      <c r="M17" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="N17" s="40"/>
+        <v>88</v>
+      </c>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="70"/>
+      <c r="N17" s="70" t="s">
+        <v>529</v>
+      </c>
       <c r="O17" s="40" t="s">
-        <v>170</v>
-      </c>
-      <c r="P17" s="40" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" s="30" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="R17" s="40" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" s="30" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E18" s="40"/>
       <c r="F18" s="40"/>
       <c r="G18" s="40"/>
-      <c r="H18" s="40" t="s">
-        <v>39</v>
-      </c>
+      <c r="H18" s="40"/>
       <c r="I18" s="40"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="70" t="s">
-        <v>534</v>
-      </c>
-      <c r="M18" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="N18" s="40"/>
-      <c r="O18" s="40"/>
-      <c r="P18" s="42"/>
-    </row>
-    <row r="19" spans="1:16" s="30" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="J18" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" s="40"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="70" t="s">
+        <v>530</v>
+      </c>
+      <c r="O18" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="40"/>
+      <c r="R18" s="42"/>
+    </row>
+    <row r="19" spans="1:18" s="30" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E19" s="40"/>
       <c r="F19" s="40"/>
       <c r="G19" s="40"/>
-      <c r="H19" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="45" t="s">
-        <v>535</v>
-      </c>
-      <c r="L19" s="70" t="s">
-        <v>536</v>
-      </c>
-      <c r="M19" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="N19" s="40"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="42"/>
-    </row>
-    <row r="20" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="45" t="s">
+        <v>531</v>
+      </c>
+      <c r="N19" s="70" t="s">
+        <v>532</v>
+      </c>
+      <c r="O19" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="42"/>
+    </row>
+    <row r="20" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C20" s="40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D20" s="40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E20" s="40"/>
       <c r="F20" s="40"/>
       <c r="G20" s="40"/>
-      <c r="H20" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="70"/>
-      <c r="L20" s="70" t="s">
-        <v>542</v>
-      </c>
-      <c r="M20" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="N20" s="40"/>
-      <c r="O20" s="40"/>
-      <c r="P20" s="42"/>
-    </row>
-    <row r="21" spans="1:16" s="30" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="70"/>
+      <c r="N20" s="70" t="s">
+        <v>538</v>
+      </c>
+      <c r="O20" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="P20" s="40"/>
+      <c r="Q20" s="40"/>
+      <c r="R20" s="42"/>
+    </row>
+    <row r="21" spans="1:18" s="30" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21" s="40"/>
       <c r="D21" s="40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E21" s="40"/>
       <c r="F21" s="40"/>
@@ -7622,59 +7845,63 @@
       <c r="H21" s="40"/>
       <c r="I21" s="40"/>
       <c r="J21" s="40"/>
-      <c r="K21" s="41"/>
-      <c r="L21" s="41" t="s">
-        <v>543</v>
-      </c>
-      <c r="M21" s="40" t="s">
-        <v>147</v>
-      </c>
-      <c r="N21" s="40"/>
-      <c r="O21" s="40"/>
-      <c r="P21" s="42"/>
-    </row>
-    <row r="22" spans="1:16" s="30" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="41" t="s">
+        <v>539</v>
+      </c>
+      <c r="O21" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="40"/>
+      <c r="R21" s="42"/>
+    </row>
+    <row r="22" spans="1:18" s="30" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39"/>
       <c r="B22" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C22" s="40"/>
       <c r="D22" s="40" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F22" s="40"/>
       <c r="G22" s="40"/>
-      <c r="H22" s="40" t="s">
-        <v>124</v>
-      </c>
+      <c r="H22" s="40"/>
       <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="41"/>
-      <c r="L22" s="41" t="s">
-        <v>545</v>
-      </c>
-      <c r="M22" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="N22" s="40" t="s">
-        <v>180</v>
-      </c>
-      <c r="O22" s="40"/>
-      <c r="P22" s="42"/>
-    </row>
-    <row r="23" spans="1:16" s="30" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J22" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="K22" s="40"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41" t="s">
+        <v>541</v>
+      </c>
+      <c r="O22" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="P22" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q22" s="40"/>
+      <c r="R22" s="42"/>
+    </row>
+    <row r="23" spans="1:18" s="30" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C23" s="40"/>
       <c r="D23" s="40" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E23" s="40"/>
       <c r="F23" s="40"/>
@@ -7682,29 +7909,31 @@
       <c r="H23" s="40"/>
       <c r="I23" s="40"/>
       <c r="J23" s="40"/>
-      <c r="K23" s="41" t="s">
-        <v>381</v>
-      </c>
-      <c r="L23" s="41" t="s">
-        <v>544</v>
-      </c>
-      <c r="M23" s="40" t="s">
-        <v>148</v>
-      </c>
-      <c r="N23" s="40"/>
-      <c r="O23" s="40"/>
-      <c r="P23" s="42"/>
-    </row>
-    <row r="24" spans="1:16" s="30" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="K23" s="40"/>
+      <c r="L23" s="40"/>
+      <c r="M23" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="N23" s="41" t="s">
+        <v>540</v>
+      </c>
+      <c r="O23" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="P23" s="40"/>
+      <c r="Q23" s="40"/>
+      <c r="R23" s="42"/>
+    </row>
+    <row r="24" spans="1:18" s="30" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C24" s="40"/>
       <c r="D24" s="40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E24" s="40"/>
       <c r="F24" s="40"/>
@@ -7712,227 +7941,247 @@
       <c r="H24" s="40"/>
       <c r="I24" s="40"/>
       <c r="J24" s="40"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="41" t="s">
-        <v>546</v>
-      </c>
-      <c r="M24" s="40" t="s">
-        <v>149</v>
-      </c>
-      <c r="N24" s="40"/>
-      <c r="O24" s="40"/>
-      <c r="P24" s="42"/>
-    </row>
-    <row r="25" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K24" s="40"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="41"/>
+      <c r="N24" s="41" t="s">
+        <v>542</v>
+      </c>
+      <c r="O24" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="42"/>
+    </row>
+    <row r="25" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C25" s="40"/>
       <c r="D25" s="40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E25" s="40"/>
       <c r="F25" s="40"/>
       <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
+      <c r="H25" s="40" t="s">
+        <v>552</v>
+      </c>
       <c r="I25" s="40"/>
       <c r="J25" s="40"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="40" t="s">
-        <v>150</v>
-      </c>
-      <c r="N25" s="40"/>
-      <c r="O25" s="40"/>
-      <c r="P25" s="42"/>
-    </row>
-    <row r="26" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K25" s="40"/>
+      <c r="L25" s="40"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="P25" s="40"/>
+      <c r="Q25" s="40"/>
+      <c r="R25" s="42"/>
+    </row>
+    <row r="26" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C26" s="40"/>
       <c r="D26" s="40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E26" s="40"/>
       <c r="F26" s="40"/>
       <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
+      <c r="H26" s="40" t="s">
+        <v>552</v>
+      </c>
       <c r="I26" s="40"/>
       <c r="J26" s="40"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="41"/>
-      <c r="M26" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="N26" s="40"/>
-      <c r="O26" s="40"/>
-      <c r="P26" s="42"/>
-    </row>
-    <row r="27" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K26" s="40"/>
+      <c r="L26" s="40"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="P26" s="40"/>
+      <c r="Q26" s="40"/>
+      <c r="R26" s="42"/>
+    </row>
+    <row r="27" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C27" s="40"/>
       <c r="D27" s="40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E27" s="40"/>
       <c r="F27" s="40"/>
       <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
+      <c r="H27" s="40" t="s">
+        <v>552</v>
+      </c>
       <c r="I27" s="40"/>
       <c r="J27" s="40"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
-      <c r="M27" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="N27" s="40"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="42"/>
-    </row>
-    <row r="28" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K27" s="40"/>
+      <c r="L27" s="40"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="42"/>
+    </row>
+    <row r="28" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="39"/>
       <c r="B28" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C28" s="40"/>
-      <c r="D28" s="40" t="s">
-        <v>120</v>
-      </c>
+      <c r="D28" s="40"/>
       <c r="E28" s="40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F28" s="40"/>
       <c r="G28" s="40"/>
-      <c r="H28" s="40" t="s">
-        <v>124</v>
-      </c>
+      <c r="H28" s="40"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
-      <c r="M28" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="N28" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="O28" s="40"/>
-      <c r="P28" s="42"/>
-    </row>
-    <row r="29" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J28" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="K28" s="40"/>
+      <c r="L28" s="40"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="P28" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="42"/>
+    </row>
+    <row r="29" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="39"/>
       <c r="B29" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C29" s="40"/>
       <c r="D29" s="40" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F29" s="40"/>
       <c r="G29" s="40"/>
-      <c r="H29" s="40" t="s">
-        <v>124</v>
-      </c>
+      <c r="H29" s="40"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="41"/>
-      <c r="M29" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N29" s="40" t="s">
-        <v>182</v>
-      </c>
-      <c r="O29" s="40"/>
-      <c r="P29" s="42"/>
-    </row>
-    <row r="30" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J29" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="P29" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="42"/>
+    </row>
+    <row r="30" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="39"/>
       <c r="B30" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C30" s="40"/>
       <c r="D30" s="40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E30" s="40" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F30" s="40"/>
       <c r="G30" s="40"/>
-      <c r="H30" s="40" t="s">
-        <v>128</v>
-      </c>
+      <c r="H30" s="40"/>
       <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
-      <c r="K30" s="41" t="s">
-        <v>378</v>
-      </c>
-      <c r="L30" s="41"/>
-      <c r="M30" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="N30" s="40" t="s">
-        <v>184</v>
-      </c>
-      <c r="O30" s="40"/>
-      <c r="P30" s="42"/>
-    </row>
-    <row r="31" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J30" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="K30" s="40"/>
+      <c r="L30" s="40"/>
+      <c r="M30" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="N30" s="41"/>
+      <c r="O30" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="P30" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="42"/>
+    </row>
+    <row r="31" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="43"/>
       <c r="B31" s="44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C31" s="44"/>
       <c r="D31" s="44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E31" s="40" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F31" s="44"/>
       <c r="G31" s="44"/>
-      <c r="H31" s="44" t="s">
-        <v>124</v>
-      </c>
+      <c r="H31" s="44"/>
       <c r="I31" s="44"/>
-      <c r="J31" s="44"/>
-      <c r="K31" s="45" t="s">
-        <v>379</v>
-      </c>
-      <c r="L31" s="45"/>
-      <c r="M31" s="44" t="s">
+      <c r="J31" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="N31" s="40" t="s">
-        <v>183</v>
-      </c>
-      <c r="O31" s="44"/>
-      <c r="P31" s="72"/>
-    </row>
-    <row r="32" spans="1:16" s="30" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="K31" s="44"/>
+      <c r="L31" s="44"/>
+      <c r="M31" s="45" t="s">
+        <v>375</v>
+      </c>
+      <c r="N31" s="45"/>
+      <c r="O31" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="P31" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="72"/>
+    </row>
+    <row r="32" spans="1:18" s="30" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="43"/>
       <c r="B32" s="44" t="s">
         <v>5</v>
       </c>
       <c r="C32" s="44"/>
       <c r="D32" s="44" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E32" s="44"/>
       <c r="F32" s="44"/>
@@ -7940,131 +8189,141 @@
       <c r="H32" s="44"/>
       <c r="I32" s="44"/>
       <c r="J32" s="44"/>
-      <c r="K32" s="45" t="s">
-        <v>380</v>
-      </c>
-      <c r="L32" s="45"/>
-      <c r="M32" s="44" t="s">
-        <v>185</v>
-      </c>
-      <c r="N32" s="44"/>
-      <c r="O32" s="44"/>
-      <c r="P32" s="72"/>
-    </row>
-    <row r="33" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K32" s="44"/>
+      <c r="L32" s="44"/>
+      <c r="M32" s="45" t="s">
+        <v>376</v>
+      </c>
+      <c r="N32" s="45"/>
+      <c r="O32" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="P32" s="44"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="72"/>
+    </row>
+    <row r="33" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="44" t="s">
         <v>51</v>
-      </c>
-      <c r="B33" s="44" t="s">
-        <v>52</v>
       </c>
       <c r="C33" s="44"/>
       <c r="D33" s="40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F33" s="44"/>
       <c r="G33" s="44"/>
       <c r="H33" s="44"/>
-      <c r="I33" s="44" t="s">
-        <v>278</v>
-      </c>
-      <c r="J33" s="44" t="s">
-        <v>213</v>
-      </c>
-      <c r="K33" s="45" t="s">
-        <v>381</v>
-      </c>
-      <c r="L33" s="45"/>
-      <c r="M33" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="N33" s="44" t="s">
-        <v>218</v>
-      </c>
-      <c r="O33" s="44"/>
-      <c r="P33" s="72"/>
-    </row>
-    <row r="34" spans="1:16" s="30" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I33" s="44"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="L33" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="M33" s="45" t="s">
+        <v>377</v>
+      </c>
+      <c r="N33" s="45"/>
+      <c r="O33" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="P33" s="44" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q33" s="44"/>
+      <c r="R33" s="72"/>
+    </row>
+    <row r="34" spans="1:18" s="30" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="44" t="s">
         <v>51</v>
-      </c>
-      <c r="B34" s="44" t="s">
-        <v>52</v>
       </c>
       <c r="C34" s="40"/>
       <c r="D34" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F34" s="40"/>
       <c r="G34" s="40"/>
       <c r="H34" s="40"/>
-      <c r="I34" s="45" t="s">
-        <v>279</v>
-      </c>
-      <c r="J34" s="41" t="s">
-        <v>215</v>
-      </c>
-      <c r="K34" s="45"/>
-      <c r="L34" s="45"/>
-      <c r="M34" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="N34" s="44" t="s">
-        <v>219</v>
-      </c>
-      <c r="O34" s="40"/>
-      <c r="P34" s="42"/>
-    </row>
-    <row r="35" spans="1:16" s="30" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I34" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="J34" s="40"/>
+      <c r="K34" s="45" t="s">
+        <v>276</v>
+      </c>
+      <c r="L34" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="M34" s="45"/>
+      <c r="N34" s="45"/>
+      <c r="O34" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="P34" s="44" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="42"/>
+    </row>
+    <row r="35" spans="1:18" s="30" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="44" t="s">
         <v>51</v>
-      </c>
-      <c r="B35" s="44" t="s">
-        <v>52</v>
       </c>
       <c r="C35" s="40"/>
       <c r="D35" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F35" s="40"/>
       <c r="G35" s="40"/>
       <c r="H35" s="40"/>
-      <c r="I35" s="41" t="s">
-        <v>217</v>
-      </c>
-      <c r="J35" s="40" t="s">
-        <v>528</v>
-      </c>
-      <c r="K35" s="45" t="s">
-        <v>380</v>
-      </c>
-      <c r="L35" s="45"/>
-      <c r="M35" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="N35" s="44" t="s">
-        <v>220</v>
-      </c>
-      <c r="O35" s="40"/>
-      <c r="P35" s="42"/>
-    </row>
-    <row r="36" spans="1:16" s="30" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="L35" s="40" t="s">
+        <v>524</v>
+      </c>
+      <c r="M35" s="45" t="s">
+        <v>376</v>
+      </c>
+      <c r="N35" s="45"/>
+      <c r="O35" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="P35" s="44" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="42"/>
+    </row>
+    <row r="36" spans="1:18" s="30" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="43"/>
       <c r="B36" s="40" t="s">
         <v>5</v>
       </c>
       <c r="C36" s="40"/>
       <c r="D36" s="40" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E36" s="40"/>
       <c r="F36" s="40"/>
@@ -8072,114 +8331,124 @@
       <c r="H36" s="40"/>
       <c r="I36" s="40"/>
       <c r="J36" s="40"/>
-      <c r="K36" s="45" t="s">
-        <v>382</v>
-      </c>
-      <c r="L36" s="45"/>
-      <c r="M36" s="40" t="s">
-        <v>186</v>
-      </c>
-      <c r="N36" s="40"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="42"/>
-    </row>
-    <row r="37" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K36" s="40"/>
+      <c r="L36" s="40"/>
+      <c r="M36" s="45" t="s">
+        <v>378</v>
+      </c>
+      <c r="N36" s="45"/>
+      <c r="O36" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="42"/>
+    </row>
+    <row r="37" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="40" t="s">
         <v>51</v>
-      </c>
-      <c r="B37" s="40" t="s">
-        <v>52</v>
       </c>
       <c r="C37" s="40"/>
       <c r="D37" s="40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F37" s="40"/>
       <c r="G37" s="40"/>
       <c r="H37" s="40"/>
       <c r="I37" s="40"/>
       <c r="J37" s="40"/>
-      <c r="K37" s="45" t="s">
-        <v>383</v>
-      </c>
-      <c r="L37" s="45"/>
-      <c r="M37" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="N37" s="44" t="s">
-        <v>221</v>
-      </c>
-      <c r="O37" s="40"/>
-      <c r="P37" s="42"/>
-    </row>
-    <row r="38" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K37" s="40"/>
+      <c r="L37" s="40"/>
+      <c r="M37" s="45" t="s">
+        <v>379</v>
+      </c>
+      <c r="N37" s="45"/>
+      <c r="O37" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="P37" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="42"/>
+    </row>
+    <row r="38" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" s="40" t="s">
         <v>51</v>
-      </c>
-      <c r="B38" s="40" t="s">
-        <v>52</v>
       </c>
       <c r="C38" s="40"/>
       <c r="D38" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F38" s="40"/>
       <c r="G38" s="40"/>
       <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
+      <c r="I38" s="40" t="s">
+        <v>550</v>
+      </c>
       <c r="J38" s="40"/>
-      <c r="K38" s="41"/>
-      <c r="L38" s="41"/>
-      <c r="M38" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="N38" s="44" t="s">
-        <v>222</v>
-      </c>
-      <c r="O38" s="40"/>
-      <c r="P38" s="42"/>
-    </row>
-    <row r="39" spans="1:16" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K38" s="40"/>
+      <c r="L38" s="40"/>
+      <c r="M38" s="41"/>
+      <c r="N38" s="41"/>
+      <c r="O38" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="P38" s="44" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="42"/>
+    </row>
+    <row r="39" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="44" t="s">
         <v>51</v>
-      </c>
-      <c r="B39" s="40" t="s">
-        <v>52</v>
       </c>
       <c r="C39" s="44"/>
       <c r="D39" s="44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F39" s="44"/>
       <c r="G39" s="44"/>
       <c r="H39" s="44"/>
       <c r="I39" s="44"/>
       <c r="J39" s="44"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="45"/>
-      <c r="M39" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="N39" s="44" t="s">
-        <v>223</v>
-      </c>
-      <c r="O39" s="44"/>
-      <c r="P39" s="72"/>
+      <c r="K39" s="44"/>
+      <c r="L39" s="44"/>
+      <c r="M39" s="45"/>
+      <c r="N39" s="45"/>
+      <c r="O39" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="P39" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q39" s="44"/>
+      <c r="R39" s="72"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError sqref="B3:B31 B32:B39" numberStoredAsText="1"/>
+    <ignoredError sqref="B3:B31 B32:B39 I11 I6 I34 I38" numberStoredAsText="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
@@ -8204,7 +8473,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -8212,7 +8481,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -8246,74 +8515,74 @@
         <v>12</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1" s="23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E4" s="18"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="C5" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="D5" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" s="26" t="s">
         <v>126</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -8338,7 +8607,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -8346,7 +8615,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -8369,74 +8638,74 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="C1" s="34" t="s">
         <v>190</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="B2" s="36" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="C2" s="37" t="s">
         <v>193</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C3" s="35" t="s">
         <v>199</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="C3" s="35" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="30" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="30" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" s="36" t="s">
         <v>195</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>196</v>
       </c>
       <c r="C6" s="36"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="36" t="s">
         <v>197</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>198</v>
       </c>
       <c r="C7" s="36"/>
     </row>
@@ -8462,7 +8731,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -8470,7 +8739,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/tools/example_framework.xlsx
+++ b/tools/example_framework.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\tarkadia\projects\intuitem\ciso-assistant-community\tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E84F6D-1951-4647-B96B-120B76A95CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1C6024-1613-47E4-AAEF-428390C867CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1485" yWindow="-15870" windowWidth="25440" windowHeight="15990" tabRatio="907" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,32 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0" shapeId="0" xr:uid="{8377CD80-173C-4910-ABAF-16B301C42544}">
+    <comment ref="A11" authorId="0" shapeId="0" xr:uid="{FCDB3F77-8B06-4998-BCDC-B60DCE09EC36}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">.: About label :.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Works like the hashtag system in social media. Labels mustn't contains spaces. They are  separated by line breaks or commas.
+All labels will be forced to uppercase in the resulting YAML file.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{8377CD80-173C-4910-ABAF-16B301C42544}">
       <text>
         <r>
           <rPr>
@@ -666,7 +691,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="555">
   <si>
     <t>type</t>
   </si>
@@ -2541,12 +2566,18 @@
   <si>
     <t>nice_to_have</t>
   </si>
+  <si>
+    <t>labels</t>
+  </si>
+  <si>
+    <t>example_framework, framework1, my-very-cool-framework, I-LOVE-MY-FRAMEWORK</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2719,6 +2750,13 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="18">
@@ -3255,6 +3293,24 @@
     <xf numFmtId="0" fontId="13" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3308,24 +3364,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4820,55 +4858,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="62.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="114"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="96"/>
     </row>
     <row r="2" spans="1:13" ht="42.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="97" t="s">
         <v>544</v>
       </c>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="117"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="99"/>
     </row>
     <row r="3" spans="1:13" ht="34.799999999999997" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="94" t="s">
+      <c r="A3" s="100" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="95"/>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
-      <c r="M3" s="96"/>
+      <c r="B3" s="101"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="101"/>
+      <c r="L3" s="101"/>
+      <c r="M3" s="102"/>
     </row>
     <row r="4" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="85" t="s">
@@ -5042,50 +5080,50 @@
       <c r="M12" s="81"/>
     </row>
     <row r="13" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="97" t="s">
+      <c r="A13" s="103" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="97"/>
-      <c r="C13" s="98" t="s">
+      <c r="B13" s="103"/>
+      <c r="C13" s="104" t="s">
         <v>543</v>
       </c>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="99"/>
-      <c r="I13" s="99"/>
-      <c r="J13" s="99"/>
-      <c r="K13" s="99"/>
-      <c r="L13" s="99"/>
-      <c r="M13" s="99"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="105"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="105"/>
+      <c r="M13" s="105"/>
     </row>
     <row r="14" spans="1:13" ht="34.799999999999997" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="94" t="s">
+      <c r="A14" s="100" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="95"/>
-      <c r="K14" s="95"/>
-      <c r="L14" s="95"/>
-      <c r="M14" s="96"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="101"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="101"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="101"/>
+      <c r="I14" s="101"/>
+      <c r="J14" s="101"/>
+      <c r="K14" s="101"/>
+      <c r="L14" s="101"/>
+      <c r="M14" s="102"/>
     </row>
     <row r="15" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="109" t="s">
+      <c r="A15" s="115" t="s">
         <v>258</v>
       </c>
-      <c r="B15" s="110"/>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="111"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="117"/>
       <c r="G15" s="79" t="s">
         <v>263</v>
       </c>
@@ -5116,14 +5154,14 @@
       <c r="M16" s="81"/>
     </row>
     <row r="17" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="106" t="s">
+      <c r="A17" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="107"/>
-      <c r="C17" s="107"/>
-      <c r="D17" s="107"/>
-      <c r="E17" s="107"/>
-      <c r="F17" s="108"/>
+      <c r="B17" s="113"/>
+      <c r="C17" s="113"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="113"/>
+      <c r="F17" s="114"/>
       <c r="G17" s="79" t="s">
         <v>260</v>
       </c>
@@ -5135,14 +5173,14 @@
       <c r="M17" s="81"/>
     </row>
     <row r="18" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="103" t="s">
+      <c r="A18" s="109" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="104"/>
-      <c r="C18" s="104"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="105"/>
+      <c r="B18" s="110"/>
+      <c r="C18" s="110"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="111"/>
       <c r="G18" s="79" t="s">
         <v>261</v>
       </c>
@@ -5154,14 +5192,14 @@
       <c r="M18" s="81"/>
     </row>
     <row r="19" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="100" t="s">
+      <c r="A19" s="106" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="101"/>
-      <c r="C19" s="101"/>
-      <c r="D19" s="101"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="102"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="107"/>
+      <c r="F19" s="108"/>
       <c r="G19" s="79" t="s">
         <v>47</v>
       </c>
@@ -5173,23 +5211,23 @@
       <c r="M19" s="81"/>
     </row>
     <row r="20" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="103" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="97"/>
-      <c r="C20" s="98" t="s">
+      <c r="B20" s="103"/>
+      <c r="C20" s="104" t="s">
         <v>262</v>
       </c>
-      <c r="D20" s="99"/>
-      <c r="E20" s="99"/>
-      <c r="F20" s="99"/>
-      <c r="G20" s="99"/>
-      <c r="H20" s="99"/>
-      <c r="I20" s="99"/>
-      <c r="J20" s="99"/>
-      <c r="K20" s="99"/>
-      <c r="L20" s="99"/>
-      <c r="M20" s="99"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="105"/>
+      <c r="K20" s="105"/>
+      <c r="L20" s="105"/>
+      <c r="M20" s="105"/>
     </row>
     <row r="21" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -6824,7 +6862,7 @@
   <sheetPr codeName="Feuil2">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -6913,33 +6951,41 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="78" t="s">
+        <v>553</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="78" t="s">
         <v>535</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B12" s="31" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="36" t="s">
+      <c r="B13" s="36" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+    <row r="14" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="37" t="s">
+      <c r="B14" s="37" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="36" t="s">
+      <c r="B15" s="36" t="s">
         <v>23</v>
       </c>
     </row>
